--- a/artfynd/A 61510-2020 artfynd.xlsx
+++ b/artfynd/A 61510-2020 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658555</v>
+        <v>117658570</v>
       </c>
       <c r="B4" t="n">
         <v>57287</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419381</v>
+        <v>419329</v>
       </c>
       <c r="R4" t="n">
-        <v>7051098</v>
+        <v>7051080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117658561</v>
+        <v>117658575</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>56741</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,20 +1008,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1029,17 +1029,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupsjö NV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419293</v>
+        <v>419339</v>
       </c>
       <c r="R5" t="n">
-        <v>7051356</v>
+        <v>7051204</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1084,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hörd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,7 +1218,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117658558</v>
+        <v>117658555</v>
       </c>
       <c r="B7" t="n">
         <v>57287</v>
@@ -1250,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419327</v>
+        <v>419381</v>
       </c>
       <c r="R7" t="n">
-        <v>7051182</v>
+        <v>7051098</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1298,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1325,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117658570</v>
+        <v>117658564</v>
       </c>
       <c r="B8" t="n">
         <v>57287</v>
@@ -1357,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>419329</v>
+        <v>419179</v>
       </c>
       <c r="R8" t="n">
-        <v>7051080</v>
+        <v>7051315</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117658563</v>
+        <v>117658561</v>
       </c>
       <c r="B9" t="n">
         <v>57287</v>
@@ -1464,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>419242</v>
+        <v>419293</v>
       </c>
       <c r="R9" t="n">
-        <v>7051346</v>
+        <v>7051356</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1539,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117658557</v>
+        <v>117658560</v>
       </c>
       <c r="B10" t="n">
         <v>57287</v>
@@ -1571,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419367</v>
+        <v>419348</v>
       </c>
       <c r="R10" t="n">
-        <v>7051161</v>
+        <v>7051232</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1646,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117658560</v>
+        <v>117658567</v>
       </c>
       <c r="B11" t="n">
         <v>57287</v>
@@ -1678,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>419348</v>
+        <v>419251</v>
       </c>
       <c r="R11" t="n">
-        <v>7051232</v>
+        <v>7051157</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1726,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117658564</v>
+        <v>117658569</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1785,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>419179</v>
+        <v>419321</v>
       </c>
       <c r="R12" t="n">
-        <v>7051315</v>
+        <v>7051123</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1833,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1860,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117658567</v>
+        <v>117658568</v>
       </c>
       <c r="B13" t="n">
         <v>57287</v>
@@ -1892,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419251</v>
+        <v>419294</v>
       </c>
       <c r="R13" t="n">
-        <v>7051157</v>
+        <v>7051143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1940,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1967,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117658559</v>
+        <v>117658563</v>
       </c>
       <c r="B14" t="n">
         <v>57287</v>
@@ -1999,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419332</v>
+        <v>419242</v>
       </c>
       <c r="R14" t="n">
-        <v>7051211</v>
+        <v>7051346</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2047,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117658575</v>
+        <v>117658565</v>
       </c>
       <c r="B15" t="n">
-        <v>56741</v>
+        <v>57287</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,20 +2086,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102954</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2099,25 +2107,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupsjö NV, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419339</v>
+        <v>419266</v>
       </c>
       <c r="R15" t="n">
-        <v>7051204</v>
+        <v>7051168</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hörd</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,7 +2181,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117658569</v>
+        <v>117658558</v>
       </c>
       <c r="B16" t="n">
         <v>57287</v>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419321</v>
+        <v>419327</v>
       </c>
       <c r="R16" t="n">
-        <v>7051123</v>
+        <v>7051182</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,7 +2288,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117658568</v>
+        <v>117658557</v>
       </c>
       <c r="B17" t="n">
         <v>57287</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419294</v>
+        <v>419367</v>
       </c>
       <c r="R17" t="n">
-        <v>7051143</v>
+        <v>7051161</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117658565</v>
+        <v>117658559</v>
       </c>
       <c r="B18" t="n">
         <v>57287</v>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>419266</v>
+        <v>419332</v>
       </c>
       <c r="R18" t="n">
-        <v>7051168</v>
+        <v>7051211</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 61510-2020 artfynd.xlsx
+++ b/artfynd/A 61510-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117658566</v>
+        <v>117658570</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419268</v>
+        <v>419329</v>
       </c>
       <c r="R2" t="n">
-        <v>7051177</v>
+        <v>7051080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117658571</v>
+        <v>117658575</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>56742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102954</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupsjö NV, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419294</v>
+        <v>419339</v>
       </c>
       <c r="R3" t="n">
-        <v>7051261</v>
+        <v>7051204</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hörd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658570</v>
+        <v>117658563</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419329</v>
+        <v>419242</v>
       </c>
       <c r="R4" t="n">
-        <v>7051080</v>
+        <v>7051346</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117658575</v>
+        <v>117658566</v>
       </c>
       <c r="B5" t="n">
-        <v>56741</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,20 +1016,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1029,25 +1037,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupsjö NV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419339</v>
+        <v>419268</v>
       </c>
       <c r="R5" t="n">
-        <v>7051204</v>
+        <v>7051177</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hörd</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117658562</v>
+        <v>117658565</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>419250</v>
+        <v>419266</v>
       </c>
       <c r="R6" t="n">
-        <v>7051350</v>
+        <v>7051168</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117658555</v>
+        <v>117658558</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>419381</v>
+        <v>419327</v>
       </c>
       <c r="R7" t="n">
-        <v>7051098</v>
+        <v>7051182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117658564</v>
+        <v>117658567</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>419179</v>
+        <v>419251</v>
       </c>
       <c r="R8" t="n">
-        <v>7051315</v>
+        <v>7051157</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117658561</v>
+        <v>117658569</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>419293</v>
+        <v>419321</v>
       </c>
       <c r="R9" t="n">
-        <v>7051356</v>
+        <v>7051123</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117658560</v>
+        <v>117658557</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419348</v>
+        <v>419367</v>
       </c>
       <c r="R10" t="n">
-        <v>7051232</v>
+        <v>7051161</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117658567</v>
+        <v>117658559</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>419251</v>
+        <v>419332</v>
       </c>
       <c r="R11" t="n">
-        <v>7051157</v>
+        <v>7051211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117658569</v>
+        <v>117658555</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>419321</v>
+        <v>419381</v>
       </c>
       <c r="R12" t="n">
-        <v>7051123</v>
+        <v>7051098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117658568</v>
+        <v>117658564</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>419294</v>
+        <v>419179</v>
       </c>
       <c r="R13" t="n">
-        <v>7051143</v>
+        <v>7051315</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117658563</v>
+        <v>117658571</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>78482</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>419242</v>
+        <v>419294</v>
       </c>
       <c r="R14" t="n">
-        <v>7051346</v>
+        <v>7051261</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117658565</v>
+        <v>117658562</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>419266</v>
+        <v>419250</v>
       </c>
       <c r="R15" t="n">
-        <v>7051168</v>
+        <v>7051350</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117658558</v>
+        <v>117658568</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>419327</v>
+        <v>419294</v>
       </c>
       <c r="R16" t="n">
-        <v>7051182</v>
+        <v>7051143</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117658557</v>
+        <v>117658561</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>419367</v>
+        <v>419293</v>
       </c>
       <c r="R17" t="n">
-        <v>7051161</v>
+        <v>7051356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117658559</v>
+        <v>117658560</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>419332</v>
+        <v>419348</v>
       </c>
       <c r="R18" t="n">
-        <v>7051211</v>
+        <v>7051232</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
